--- a/AI Audit log_HoDucManh_DE190923.xlsx
+++ b/AI Audit log_HoDucManh_DE190923.xlsx
@@ -1,22 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL G3 Gaming\OneDrive\Máy tính\Ki5\SWP\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9000"/>
+    <workbookView windowWidth="23040" windowHeight="9000" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="1" r:id="rId1"/>
     <sheet name="Week 2" sheetId="4" r:id="rId2"/>
-    <sheet name="ASM1" sheetId="3" r:id="rId3"/>
+    <sheet name="Week 3" sheetId="6" r:id="rId3"/>
+    <sheet name="ASM1" sheetId="3" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -34,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="19">
   <si>
     <t>STT</t>
   </si>
@@ -64,13 +60,49 @@
   </si>
   <si>
     <t>Phản hồi: AI đề xuất luồng gồm 5 bước: (1) Nhà hàng gửi purchase request → Logistics Service nhận danh sách địa chỉ giao hàng; (2) Hệ thống gom nhóm các đơn hàng gần nhau theo khu vực (Order Grouping); (3) Gọi Google Maps Distance Matrix API để tính ma trận khoảng cách và ETA giữa các điểm; (4) Google OR-Tools chạy thuật toán VRP (Vehicle Routing Problem) để tìm lộ trình tối ưu tối thiểu hóa chi phí nhiên liệu và thời gian; (5) Kết quả trả về cho Driver dưới dạng danh sách điểm dừng theo thứ tự cùng ETA từng điểm. Quyết định: Tôi nhận thấy việc tích hợp đồng thời OR-Tools và Google Maps API trong MVP sẽ tăng độ phức tạp kỹ thuật đáng kể. Tôi quyết định ở giai đoạn đầu chỉ dùng Google Directions API để tính lộ trình đơn giản giữa các điểm, sau đó mới bổ sung OR-Tools cho bài toán tối ưu đa điểm khi hệ thống có đủ dữ liệu thực tế để kiểm chứng.</t>
+  </si>
+  <si>
+    <t>Process/Algorithm</t>
+  </si>
+  <si>
+    <t>Viết hàm Java theo mô hình MVC để lọc ra danh sách nông sản sắp hết hạn sử dụng trong hệ thống Fresh Connect.</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI viết code lấy toàn bộ dữ liệu từ SQL Server lên tầng Model, sau đó dùng một vòng lặp for chạy qua hàng ngàn bản ghi để kiểm tra ngày tháng.
+Kiểm chứng: Tôi nhận thấy thuật toán này sẽ gây tràn bộ nhớ và quá tải server khi lượng dữ liệu lớn (Oversimplification). Tôi yêu cầu AI tối ưu lại bằng cách xử lý logic ngày tháng trực tiếp bằng câu lệnh truy vấn WHERE trong SQL để chỉ kéo những dữ liệu thực sự cần thiết lên hệ thống.</t>
+  </si>
+  <si>
+    <t>Pattern Recognition</t>
+  </si>
+  <si>
+    <t>Để gửi dữ liệu nhiệt độ bảo quản nông sản theo thời gian thực từ phần cứng lên app Fresh Connect, nên cấu hình chuẩn giao tiếp nào cho mạch Arduino và module Bluetooth?</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề nghị sử dụng cấu hình Bluetooth Low Energy (BLE) với giao thức mã hóa dữ liệu nhiều lớp phức tạp dùng trong công nghiệp.
+Kiểm chứng: Dựa vào mô típ các dự án IoT tôi từng triển khai, cấu hình này quá phức tạp và dễ gây lỗi kết nối (timeout). Tôi quyết định sử dụng module thông dụng kết nối qua cổng Serial UART cơ bản, vừa đảm bảo tính ổn định vừa dễ dàng debug lỗi phần cứng.</t>
+  </si>
+  <si>
+    <t>Evaluation / AI Literacy</t>
+  </si>
+  <si>
+    <t>Tóm tắt 3 bài báo nghiên cứu về ứng dụng Computer Vision (nhận diện hình ảnh) để tự động phân loại độ chín của trái cây, nhằm tích hợp vào Fresh Connect</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI cung cấp 3 bài báo kèm tên tác giả, năm xuất bản và tóm tắt công nghệ sử dụng rất thuyết phục.
+Kiểm chứng: Khi tôi tra cứu trên IEEE Xplore và Google Scholar, 1 trong 3 bài báo hoàn toàn không tồn tại (Hallucination). Tôi quyết định loại bỏ kết quả giả mạo này, tự tìm một bài báo thực tế khác về thuật toán phân loại ảnh và yêu cầu AI tóm tắt lại dựa trên link tôi cung cấp.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-* #,##0.00\ &quot;₫&quot;_-;\-* #,##0.00\ &quot;₫&quot;_-;_-* &quot;-&quot;??\ &quot;₫&quot;_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_-* #,##0\ &quot;₫&quot;_-;\-* #,##0\ &quot;₫&quot;_-;_-* &quot;-&quot;\ &quot;₫&quot;_-;_-@_-"/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -78,16 +110,353 @@
       <charset val="163"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -95,33 +464,319 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -379,42 +1034,42 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="3"/>
   <cols>
-    <col min="2" max="2" width="24.77734375" customWidth="1"/>
-    <col min="3" max="3" width="36.88671875" customWidth="1"/>
-    <col min="4" max="4" width="72.77734375" customWidth="1"/>
+    <col min="2" max="2" width="24.7777777777778" customWidth="1"/>
+    <col min="3" max="3" width="36.8888888888889" customWidth="1"/>
+    <col min="4" max="4" width="72.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="144" x14ac:dyDescent="0.3">
-      <c r="A2" s="3">
+    <row r="2" ht="129.6" spans="1:4">
+      <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D2" s="2" t="s">
@@ -423,38 +1078,40 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="3"/>
   <cols>
-    <col min="2" max="2" width="24.77734375" customWidth="1"/>
-    <col min="3" max="3" width="36.88671875" customWidth="1"/>
-    <col min="4" max="4" width="72.77734375" customWidth="1"/>
+    <col min="2" max="2" width="24.7777777777778" customWidth="1"/>
+    <col min="3" max="3" width="36.8888888888889" customWidth="1"/>
+    <col min="4" max="4" width="72.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="3">
+    <row r="2" ht="144" spans="1:4">
+      <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -466,14 +1123,90 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="3"/>
+  <cols>
+    <col min="2" max="2" width="24.7777777777778" customWidth="1"/>
+    <col min="3" max="3" width="36.8888888888889" customWidth="1"/>
+    <col min="4" max="4" width="72.7777777777778" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" ht="115.2" spans="1:4">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" ht="100.8" spans="1:4">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" ht="115.2" spans="1:4">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/AI Audit log_HoDucManh_DE190923.xlsx
+++ b/AI Audit log_HoDucManh_DE190923.xlsx
@@ -4,13 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000" activeTab="2"/>
+    <workbookView windowWidth="11520" windowHeight="8280" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="1" r:id="rId1"/>
     <sheet name="Week 2" sheetId="4" r:id="rId2"/>
     <sheet name="Week 3" sheetId="6" r:id="rId3"/>
-    <sheet name="ASM1" sheetId="3" r:id="rId4"/>
+    <sheet name="Week 4" sheetId="7" r:id="rId4"/>
+    <sheet name="ASM1" sheetId="3" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="28">
   <si>
     <t>STT</t>
   </si>
@@ -90,6 +91,35 @@
   <si>
     <t>Phản hồi: AI cung cấp 3 bài báo kèm tên tác giả, năm xuất bản và tóm tắt công nghệ sử dụng rất thuyết phục.
 Kiểm chứng: Khi tôi tra cứu trên IEEE Xplore và Google Scholar, 1 trong 3 bài báo hoàn toàn không tồn tại (Hallucination). Tôi quyết định loại bỏ kết quả giả mạo này, tự tìm một bài báo thực tế khác về thuật toán phân loại ảnh và yêu cầu AI tóm tắt lại dựa trên link tôi cung cấp.</t>
+  </si>
+  <si>
+    <t>Decomposition</t>
+  </si>
+  <si>
+    <t>Viết mã HTML, CSS và JavaScript cho giao diện trang chủ Fresh Connect, bao gồm thanh điều hướng, banner động, danh sách sản phẩm nổi bật và phần đánh giá của khách hàng</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI trả về một khối code khổng lồ, trộn lẫn cả logic JavaScript vào trong file HTML và sử dụng hàng loạt style nội tuyến (inline style).
+Quyết định: Khối code này rất khó đọc và không thể tái sử dụng cho các trang khác. Tôi yêu cầu AI phân rã (Decomposition) cấu trúc giao diện thành các Component riêng biệt (Header, Banner, ProductCard, Footer) và tách riêng file .css, .js để dễ dàng quản lý source code.</t>
+  </si>
+  <si>
+    <t>Logic / Debugging</t>
+  </si>
+  <si>
+    <t>Sửa lỗi hàm calculateTotal() trong giỏ hàng. Khi khách hàng thêm mã giảm giá 20%, tổng tiền bị tính sai thành số âm đối với các đơn hàng có giá trị nhỏ.</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI cung cấp đoạn code kiểm tra: if (total - discount &lt; 0) total = 0; để ngăn số âm.
+Kiểm chứng: Cách giải quyết này chỉ che đậy lỗi hiển thị mà không xử lý sai sót về mặt nghiệp vụ (Logic error). Lỗi thực sự nằm ở việc tính toán chiết khấu trên từng sản phẩm chưa chính xác. Tôi quyết định tự viết lại logic tính toán, áp dụng chiết khấu dựa trên giá trị gốc của giỏ hàng trước khi cộng phí vận chuyển để đảm bảo tính minh bạch về tài chính.</t>
+  </si>
+  <si>
+    <t>Optimization / Security</t>
+  </si>
+  <si>
+    <t>Làm thế nào để đưa dự án Fresh Connect (Java Spring Boot, SQL Server) lên một server để mọi người có thể truy cập được? Cung cấp các bước thực hiện nhanh nhất</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI hướng dẫn thuê VPS, tắt tường lửa (Firewall) cho nhanh, cài đặt SQL Server chung với ứng dụng, và mở cổng (port) database ra ngoài Internet để dễ kết nối từ xa.Kiểm chứng: Tôi nhận thấy việc tắt tường lửa và mở cổng database công khai là một lỗ hổng bảo mật cực kỳ nghiêm trọng (Harmful advice). Tôi quyết định từ chối phương pháp này. Thay vào đó, tôi tự tìm hiểu và triển khai hệ thống theo mô hình Docker Containers, đặt database trong mạng nội bộ (private network) và chỉ mở cổng web (port 80/443) ra ngoài.</t>
   </si>
 </sst>
 </file>
@@ -1203,6 +1233,79 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="3"/>
+  <cols>
+    <col min="2" max="2" width="24.7777777777778" customWidth="1"/>
+    <col min="3" max="3" width="36.8888888888889" customWidth="1"/>
+    <col min="4" max="4" width="72.7777777777778" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" ht="115.2" spans="1:4">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" ht="129.6" spans="1:4">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" ht="100.8" spans="1:4">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>

--- a/AI Audit log_HoDucManh_DE190923.xlsx
+++ b/AI Audit log_HoDucManh_DE190923.xlsx
@@ -4,14 +4,15 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="11520" windowHeight="8280" activeTab="3"/>
+    <workbookView windowWidth="23040" windowHeight="8940" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="1" r:id="rId1"/>
     <sheet name="Week 2" sheetId="4" r:id="rId2"/>
     <sheet name="Week 3" sheetId="6" r:id="rId3"/>
     <sheet name="Week 4" sheetId="7" r:id="rId4"/>
-    <sheet name="ASM1" sheetId="3" r:id="rId5"/>
+    <sheet name="Week 5" sheetId="8" r:id="rId5"/>
+    <sheet name="ASM1" sheetId="3" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="39">
   <si>
     <t>STT</t>
   </si>
@@ -120,6 +121,39 @@
   </si>
   <si>
     <t>Phản hồi: AI hướng dẫn thuê VPS, tắt tường lửa (Firewall) cho nhanh, cài đặt SQL Server chung với ứng dụng, và mở cổng (port) database ra ngoài Internet để dễ kết nối từ xa.Kiểm chứng: Tôi nhận thấy việc tắt tường lửa và mở cổng database công khai là một lỗ hổng bảo mật cực kỳ nghiêm trọng (Harmful advice). Tôi quyết định từ chối phương pháp này. Thay vào đó, tôi tự tìm hiểu và triển khai hệ thống theo mô hình Docker Containers, đặt database trong mạng nội bộ (private network) và chỉ mở cổng web (port 80/443) ra ngoài.</t>
+  </si>
+  <si>
+    <t>Database Design / Data Modeling</t>
+  </si>
+  <si>
+    <t>Viết mã SQL để tạo bảng InventoryStocks và InventoryMovements cho hệ thống Fresh Connect, đảm bảo có khóa ngoại liên kết với bảng Products và Suppliers.</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI cung cấp script SQL tạo bảng cơ bản với các cột khóa chính, khóa ngoại (ProductId, SupplierId) theo chuẩn. Kiểm chứng: Dựa vào tài liệu thiết kế cơ sở dữ liệu và Business Rule BR-33 (Số lượng tồn kho không được âm và phải phản ánh thực tế), tôi nhận thấy script của AI thiếu ràng buộc kiểm tra giá trị.   Quyết định: Tôi tự quyết định bổ sung thêm ràng buộc CHECK (Quantity &gt;= 0) vào script SQL của AI và thêm Index cho các cột khóa ngoại để tối ưu hóa tốc độ truy vấn khi hiển thị Inventory Overview.</t>
+  </si>
+  <si>
+    <t>Component Decomposition / UI Design</t>
+  </si>
+  <si>
+    <t>Dựa vào yêu cầu thiết kế UI của màn hình Delivery Tracking Screen, hãy phân rã các component ReactJS cần thiết và viết code giao diện cho phần Delivery Actions bao gồm các nút: Confirm Receipt, Report Issue, và Evaluate Delivery.</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI phân rã màn hình thành các component hợp lý và cung cấp code tĩnh (static UI) với 3 nút bấm luôn hiển thị cạnh nhau.   Kiểm chứng: Mặc dù code UI đẹp, nhưng việc hiển thị cả 3 nút bấm cùng lúc là lỗi về mặt Logic (Logic error). Theo quy trình nghiệp vụ (BR-24, BR-53), nút "Confirm Receipt" hoặc "Evaluate" chỉ được phép tương tác khi trạng thái giao hàng là đã đến nơi.   Quyết định: Tôi yêu cầu AI sửa lại code, truyền thêm deliveryStatus vào Component (Props) và sử dụng toán tử điều kiện (Conditional Rendering) để ẩn/hiện các nút hành động này dựa trên trạng thái giao hàng thực tế.</t>
+  </si>
+  <si>
+    <t>Business Logic / Backend</t>
+  </si>
+  <si>
+    <t>Viết một hàm xử lý nghiệp vụ (Service layer) bằng Java Spring Boot cho chức năng Submit Purchase Request (UC-15). Khi Restaurant Manager nhấn Submit, hệ thống cần thực hiện những bước nào?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phản hồi: AI viết hàm tìm kiếm Purchase Request theo ID, sau đó cập nhật trực tiếp trường Status thành "Submitted" và lưu vào cơ sở dữ liệu.   Kiểm chứng: Cách giải quyết này thiếu kiểm duyệt nghiệp vụ nghiêm trọng. Theo tài liệu (BR-16 và BR-17), một yêu cầu mua hàng (Draft) bắt buộc phải có ít nhất một sản phẩm hợp lệ bên trong trước khi được submit.   Quyết định: Tôi không dùng nguyên bản code của AI. Tôi tự viết thêm một vòng lặp logic để kiểm tra danh sách PurchaseRequestItems. Nếu danh sách rỗng hoặc số lượng = 0, hệ thống phải throw Exception (báo lỗi) và chặn thao tác Submit để đảm bảo tính toàn vẹn dữ liệu.  </t>
+  </si>
+  <si>
+    <t>Làm thế nào để phân quyền (Authorization) API trong hệ thống Fresh Connect để đảm bảo Restaurant Manager chỉ xem được dữ liệu dashboard của nhà hàng mình (BR-12) và Supplier chỉ xem được đơn mua hàng gửi cho họ (BR-35)?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phản hồi: AI đề xuất sử dụng Spring Security để phân quyền dựa trên Role (Role-based access control), ví dụ dùng annotation @PreAuthorize("hasRole('RESTAURANT_MANAGER')") trên các endpoint.Kiểm chứng: Lời khuyên này sinh ra lỗ hổng bảo mật IDOR (Insecure Direct Object Reference). Việc chỉ kiểm tra Role là không đủ để đáp ứng quy tắc BR-12 (Own Data Access Control) và BR-35 (Request Visibility). Một quản lý nhà hàng vẫn có thể truyền ID của nhà hàng khác vào API để xem trộm dữ liệu.   Quyết định: Tôi từ chối giải pháp này. Tôi tự tìm hiểu và triển khai cơ chế kiểm tra bảo mật cấp độ bản ghi (Record-level security): Trích xuất UserId từ JWT Token ở Backend, truy vấn ra RestaurantId/SupplierId tương ứng, và so sánh chéo nó với dữ liệu đang được request trước khi trả kết quả về.  </t>
   </si>
 </sst>
 </file>
@@ -740,10 +774,16 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1071,11 +1111,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="1" outlineLevelCol="3"/>
   <cols>
-    <col min="2" max="2" width="24.7777777777778" customWidth="1"/>
-    <col min="3" max="3" width="36.8888888888889" customWidth="1"/>
-    <col min="4" max="4" width="72.7777777777778" customWidth="1"/>
+    <col min="2" max="2" width="24.7809523809524" customWidth="1"/>
+    <col min="3" max="3" width="36.8857142857143" customWidth="1"/>
+    <col min="4" max="4" width="72.7809523809524" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1092,17 +1132,17 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="129.6" spans="1:4">
+    <row r="2" ht="150" spans="1:4">
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="4" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1116,11 +1156,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="1" outlineLevelCol="3"/>
   <cols>
-    <col min="2" max="2" width="24.7777777777778" customWidth="1"/>
-    <col min="3" max="3" width="36.8888888888889" customWidth="1"/>
-    <col min="4" max="4" width="72.7777777777778" customWidth="1"/>
+    <col min="2" max="2" width="24.7809523809524" customWidth="1"/>
+    <col min="3" max="3" width="36.8857142857143" customWidth="1"/>
+    <col min="4" max="4" width="72.7809523809524" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1137,17 +1177,17 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="144" spans="1:4">
+    <row r="2" ht="165" spans="1:4">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="4" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1161,11 +1201,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="3" outlineLevelCol="3"/>
   <cols>
-    <col min="2" max="2" width="24.7777777777778" customWidth="1"/>
-    <col min="3" max="3" width="36.8888888888889" customWidth="1"/>
-    <col min="4" max="4" width="72.7777777777778" customWidth="1"/>
+    <col min="2" max="2" width="24.7809523809524" customWidth="1"/>
+    <col min="3" max="3" width="36.8857142857143" customWidth="1"/>
+    <col min="4" max="4" width="72.7809523809524" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1182,45 +1222,45 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="115.2" spans="1:4">
+    <row r="2" ht="120" spans="1:4">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" ht="100.8" spans="1:4">
+    <row r="3" ht="120" spans="1:4">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4" ht="115.2" spans="1:4">
+    <row r="4" ht="120" spans="1:4">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="4" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1234,11 +1274,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="3" outlineLevelCol="3"/>
   <cols>
-    <col min="2" max="2" width="24.7777777777778" customWidth="1"/>
-    <col min="3" max="3" width="36.8888888888889" customWidth="1"/>
-    <col min="4" max="4" width="72.7777777777778" customWidth="1"/>
+    <col min="2" max="2" width="24.7809523809524" customWidth="1"/>
+    <col min="3" max="3" width="36.8857142857143" customWidth="1"/>
+    <col min="4" max="4" width="72.7809523809524" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1255,45 +1295,45 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="115.2" spans="1:4">
+    <row r="2" ht="120" spans="1:4">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="3" ht="129.6" spans="1:4">
+    <row r="3" ht="135" spans="1:4">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="4" ht="100.8" spans="1:4">
+    <row r="4" ht="105" spans="1:4">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="4" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1306,8 +1346,99 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="5" outlineLevelCol="3"/>
+  <cols>
+    <col min="2" max="2" width="32" customWidth="1"/>
+    <col min="3" max="3" width="43" customWidth="1"/>
+    <col min="4" max="4" width="72.7809523809524" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" ht="114" customHeight="1" spans="1:4">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" ht="135" customHeight="1" spans="1:4">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" ht="150" customHeight="1" spans="1:4">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" ht="165" spans="1:4">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="3:4">
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/AI Audit log_HoDucManh_DE190923.xlsx
+++ b/AI Audit log_HoDucManh_DE190923.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8940" activeTab="4"/>
+    <workbookView windowWidth="24000" windowHeight="9480" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="1" r:id="rId1"/>
@@ -12,7 +12,8 @@
     <sheet name="Week 3" sheetId="6" r:id="rId3"/>
     <sheet name="Week 4" sheetId="7" r:id="rId4"/>
     <sheet name="Week 5" sheetId="8" r:id="rId5"/>
-    <sheet name="ASM1" sheetId="3" r:id="rId6"/>
+    <sheet name="Week 6" sheetId="9" r:id="rId6"/>
+    <sheet name="ASM1" sheetId="3" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="50">
   <si>
     <t>STT</t>
   </si>
@@ -154,6 +155,39 @@
   </si>
   <si>
     <t xml:space="preserve">Phản hồi: AI đề xuất sử dụng Spring Security để phân quyền dựa trên Role (Role-based access control), ví dụ dùng annotation @PreAuthorize("hasRole('RESTAURANT_MANAGER')") trên các endpoint.Kiểm chứng: Lời khuyên này sinh ra lỗ hổng bảo mật IDOR (Insecure Direct Object Reference). Việc chỉ kiểm tra Role là không đủ để đáp ứng quy tắc BR-12 (Own Data Access Control) và BR-35 (Request Visibility). Một quản lý nhà hàng vẫn có thể truyền ID của nhà hàng khác vào API để xem trộm dữ liệu.   Quyết định: Tôi từ chối giải pháp này. Tôi tự tìm hiểu và triển khai cơ chế kiểm tra bảo mật cấp độ bản ghi (Record-level security): Trích xuất UserId từ JWT Token ở Backend, truy vấn ra RestaurantId/SupplierId tương ứng, và so sánh chéo nó với dữ liệu đang được request trước khi trả kết quả về.  </t>
+  </si>
+  <si>
+    <t>Algorithm / Backend Logic</t>
+  </si>
+  <si>
+    <t>Viết logic bằng Java/Python cho chức năng View AI Demand Forecasts (UC-20) để dự báo nhu cầu nguyên liệu cho nhà hàng, lấy dữ liệu mua hàng để tính toán.</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI cung cấp một hàm tính toán trung bình động (Moving Average) cơ bản chỉ dựa trên số lượng mua của 3 tháng gần nhất.Kiểm chứng: Thuật toán của AI quá đơn giản và chưa đáp ứng đủ yêu cầu nghiệp vụ. Theo quy tắc BR-21, các mô hình dự báo bắt buộc phải sử dụng cả dữ liệu mua hàng trong quá khứ và dữ liệu vận hành (historical purchasing and operational data) để dự đoán nhu cầu trong tương lai. Việc bỏ qua các yếu tố vận hành như xu hướng thị trường hoặc quy mô nhà hàng là một thiếu sót về Logic.   Quyết định: Tôi yêu cầu AI phải tích hợp thêm thư viện học máy (Machine Learning) để có thể xem xét thêm các biến số về dữ liệu hoạt động, đảm bảo kết quả dự báo sát với thực tế hơn.</t>
+  </si>
+  <si>
+    <t>Business Logic / API Development</t>
+  </si>
+  <si>
+    <t>Viết API Java Spring Boot để xử lý chức năng Configure Recurring Orders (UC-18). Hàm sẽ nhận thông tin từ Restaurant Manager và lưu lịch mua hàng vào database.</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI tạo ra một endpoint CRUD tiêu chuẩn chỉ thực hiện việc lưu thông tin (sản phẩm, số lượng, tần suất) vào bảng cấu hình định kỳ.Kiểm chứng: Cách giải quyết này chưa hoàn thiện chức năng cốt lõi. Theo định nghĩa UC-18, hệ thống phải cho phép "tạo tự động các yêu cầu mua hàng dựa trên lịch trình đã định sẵn". Theo quy tắc BR-19, đơn hàng định kỳ phải được tạo ra (generated) theo đúng tần suất đã cấu hình. Nếu chỉ lưu database, đơn hàng sẽ không bao giờ tự động sinh ra.   Quyết định: Tôi không dùng code gốc. Tôi yêu cầu AI cung cấp thêm giải pháp sử dụng @Scheduled (Cron Job) trong Spring Boot để Backend tự động quét bảng cấu hình mỗi ngày và tự động tạo ra các PurchaseRequest ở trạng thái Draft.</t>
+  </si>
+  <si>
+    <t>Security / File Management</t>
+  </si>
+  <si>
+    <t>Viết mã ReactJS cho chức năng Report Delivery Issues (UC-25), cho phép Restaurant Manager tải lên hình ảnh minh chứng (Upload Evidence) khi hàng hóa bị hỏng hoặc giao thiếu.</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI viết một component với thẻ &lt;input type="file" /&gt; cho phép chọn mọi loại file và gọi API đẩy thẳng file nguyên bản (chưa qua kiểm tra) lên máy chủ.Kiểm chứng: Lời khuyên này sinh ra lỗ hổng bảo mật (Harmful advice). Theo giả định AS-7, các tài liệu và bằng chứng tải lên phải tuân thủ định dạng tệp được hỗ trợ và giới hạn kích thước của hệ thống. Việc cho phép tải mọi loại file có thể dẫn đến việc upload mã độc (Malicious file execution).   Quyết định: Tôi từ chối giải pháp này. Tôi tự thêm thuộc tính accept="image/png, image/jpeg" ở Frontend, giới hạn dung lượng &lt; 5MB. Đồng thời, tôi yêu cầu AI viết lại Backend để kiểm tra chặt chẽ MIME type trước khi lưu file minh chứng.</t>
+  </si>
+  <si>
+    <t>Viết mã ReactJS sử dụng Chart.js để hiển thị biểu đồ Tổng chi phí mua sắm (Total Procurement Cost) cho màn hình Restaurant Analytics Dashboard (UC-26).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phản hồi: AI đề xuất gọi API lấy toàn bộ lịch sử đơn hàng (Orders và Order_Details) của nhà hàng về Frontend, sau đó dùng JavaScript chạy vòng lặp cộng dồn tổng tiền theo từng tháng để vẽ biểu đồ.Kiểm chứng: Phương pháp này gây quá tải bộ nhớ trình duyệt và vi phạm quy trình xử lý dữ liệu (Optimization issue). Theo thiết kế luồng xử lý UC-26, hệ thống Backend mới là nơi "tính toán các số liệu mua sắm" (System calculates procurement metrics).   Quyết định: Tôi loại bỏ việc tính toán trên Frontend. Tôi tự viết một câu Query SQL sử dụng GROUP BY và hàm SUM() ở Backend để nhóm tổng chi phí theo tháng, đảm bảo chỉ trích xuất dữ liệu được ủy quyền của đúng nhà hàng đó (theo BR-27). ReactJS Frontend sau đó chỉ việc nhận chuỗi JSON nhẹ gọn và đưa vào Chart.js.  </t>
   </si>
 </sst>
 </file>
@@ -1437,6 +1471,97 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="5" outlineLevelCol="3"/>
+  <cols>
+    <col min="2" max="2" width="32" customWidth="1"/>
+    <col min="3" max="3" width="43" customWidth="1"/>
+    <col min="4" max="4" width="72.7809523809524" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" ht="142" customHeight="1" spans="1:4">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" ht="154" customHeight="1" spans="1:4">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" ht="150" customHeight="1" spans="1:4">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" ht="150" spans="1:4">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="3:4">
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <sheetData/>

--- a/AI Audit log_HoDucManh_DE190923.xlsx
+++ b/AI Audit log_HoDucManh_DE190923.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24000" windowHeight="9480" activeTab="5"/>
+    <workbookView windowWidth="12000" windowHeight="10200" firstSheet="3" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="1" r:id="rId1"/>
@@ -13,7 +13,8 @@
     <sheet name="Week 4" sheetId="7" r:id="rId4"/>
     <sheet name="Week 5" sheetId="8" r:id="rId5"/>
     <sheet name="Week 6" sheetId="9" r:id="rId6"/>
-    <sheet name="ASM1" sheetId="3" r:id="rId7"/>
+    <sheet name="Week 7" sheetId="10" r:id="rId7"/>
+    <sheet name="ASM1" sheetId="3" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="62">
   <si>
     <t>STT</t>
   </si>
@@ -188,6 +189,50 @@
   </si>
   <si>
     <t xml:space="preserve">Phản hồi: AI đề xuất gọi API lấy toàn bộ lịch sử đơn hàng (Orders và Order_Details) của nhà hàng về Frontend, sau đó dùng JavaScript chạy vòng lặp cộng dồn tổng tiền theo từng tháng để vẽ biểu đồ.Kiểm chứng: Phương pháp này gây quá tải bộ nhớ trình duyệt và vi phạm quy trình xử lý dữ liệu (Optimization issue). Theo thiết kế luồng xử lý UC-26, hệ thống Backend mới là nơi "tính toán các số liệu mua sắm" (System calculates procurement metrics).   Quyết định: Tôi loại bỏ việc tính toán trên Frontend. Tôi tự viết một câu Query SQL sử dụng GROUP BY và hàm SUM() ở Backend để nhóm tổng chi phí theo tháng, đảm bảo chỉ trích xuất dữ liệu được ủy quyền của đúng nhà hàng đó (theo BR-27). ReactJS Frontend sau đó chỉ việc nhận chuỗi JSON nhẹ gọn và đưa vào Chart.js.  </t>
+  </si>
+  <si>
+    <t>Quality Assurance / Testing</t>
+  </si>
+  <si>
+    <t>Viết Unit Test bằng JUnit 5 và Mockito cho Service xử lý chức năng Submit Purchase Request (UC-15) của Restaurant Manager, đảm bảo bao phủ cả trường hợp hợp lệ và không hợp lệ.</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI cung cấp các test case cơ bản (Happy path) để mock database và xác nhận trạng thái đơn hàng chuyển sang "Submitted" thành công.
+Kiểm chứng: Đoạn code test của AI đã bỏ sót các ngoại lệ (Edge cases) cực kỳ quan trọng về mặt nghiệp vụ. Nó không hề có test case nào để kiểm chứng việc hệ thống phải ném ra lỗi BusinessException khi giỏ hàng trống hoặc có sản phẩm số lượng bằng 0 (theo Business Rule đã phân tích ở tuần 5).
+Quyết định: Tôi yêu cầu AI viết bổ sung các test case assertThrows để bắt chặt chẽ các lỗi ngoại lệ này, đảm bảo độ bao phủ code (Code coverage) và tính chính xác của Service layer trước khi tích hợp.</t>
+  </si>
+  <si>
+    <t>System Integration / Backend</t>
+  </si>
+  <si>
+    <t>Viết logic cho hệ thống để tự động gửi thông báo (Notification) cho Restaurant Manager khi trạng thái đơn mua hàng (Purchase Request Status) được Supplier cập nhật thành "Đang giao" (Shipping).</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI viết code gọi trực tiếp hàm EmailService.sendEmail() ngay bên trong luồng (Thread) xử lý cập nhật trạng thái đơn hàng của API.
+Kiểm chứng: Việc gọi hàm gửi email đồng bộ (Synchronous) như vậy là một lỗi tối ưu hóa nghiêm trọng. Quá trình kết nối SMTP server gửi email thường mất vài giây, điều này sẽ "block" luồng chính, khiến API phản hồi rất chậm và làm trải nghiệm của người dùng bị treo (Performance issue).
+Quyết định: Tôi không sử dụng cách này. Tôi tự quyết định áp dụng cơ chế bất đồng bộ (Asynchronous) bằng cách thêm annotation @Async trong Spring Boot hoặc đẩy sự kiện gửi email vào Message Queue (RabbitMQ) để API có thể trả về kết quả ngay lập tức.</t>
+  </si>
+  <si>
+    <t>Business Logic / UI Design</t>
+  </si>
+  <si>
+    <t>Viết component ReactJS cho chức năng Đánh giá nhà cung cấp (Evaluate Supplier - UC-23). Component cần có form chấm điểm từ 1-5 sao và ô nhập nhận xét cho Restaurant Manager</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI tạo một màn hình độc lập có danh sách toàn bộ Supplier trong hệ thống và một form để Restaurant Manager có thể click vào bất kỳ Supplier nào để đánh giá.
+Kiểm chứng: Giao diện này vi phạm quy tắc nghiệp vụ (Logic error). Quản lý nhà hàng không được phép đánh giá một nhà cung cấp mà họ chưa từng giao dịch. Chức năng đánh giá phải được gắn liền với một đơn giao hàng cụ thể đã hoàn tất.
+Quyết định: Tôi yêu cầu AI làm lại. Form đánh giá không được đứng độc lập mà phải được thiết kế dưới dạng một Modal (Hộp thoại). Nút "Đánh giá" (Evaluate) chỉ được hiển thị (Conditional Rendering) bên trong chi tiết của những đơn hàng đã chuyển sang trạng thái "Delivered" hoặc "Completed".</t>
+  </si>
+  <si>
+    <t>Optimization / Database</t>
+  </si>
+  <si>
+    <t>Viết API bằng Spring Boot và Spring Data JPA để lấy toàn bộ lịch sử các Yêu cầu mua hàng (Purchase Requests) của một nhà hàng (UC-14) để hiển thị lên bảng thống kê.</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI sử dụng phương thức findAllByRestaurantId() trả về một List chứa toàn bộ dữ liệu lịch sử đơn hàng của nhà hàng đó từ trước đến nay.
+Kiểm chứng: Cách truy vấn này sẽ gây lỗi tràn bộ nhớ (Out of Memory) và sập server nếu nhà hàng hoạt động lâu năm, có hàng ngàn đơn hàng trong database (Optimization/Scalability issue).
+Quyết định: Tôi loại bỏ cách làm này. Tôi tự triển khai cơ chế Phân trang (Pagination) bằng cách sử dụng interface Pageable của Spring Data JPA. API giờ đây bắt buộc phải nhận tham số page và size (ví dụ: size=10), giúp tối ưu hóa truy vấn SQL (sử dụng LIMIT và OFFSET) và giảm tải băng thông mạng.</t>
   </si>
 </sst>
 </file>
@@ -1562,6 +1607,97 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="5" outlineLevelCol="3"/>
+  <cols>
+    <col min="2" max="2" width="32" customWidth="1"/>
+    <col min="3" max="3" width="43" customWidth="1"/>
+    <col min="4" max="4" width="72.7809523809524" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" ht="142" customHeight="1" spans="1:4">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" ht="154" customHeight="1" spans="1:4">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" ht="150" customHeight="1" spans="1:4">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" ht="135" spans="1:4">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="3:4">
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <sheetData/>
